--- a/ROI记录表.xlsx
+++ b/ROI记录表.xlsx
@@ -2582,169 +2582,265 @@
       <c r="A103" s="7">
         <v>46275</v>
       </c>
-      <c r="B103" s="3"/>
-      <c r="C103" s="3"/>
+      <c r="B103" s="3">
+        <v>10.44</v>
+      </c>
+      <c r="C103" s="3">
+        <v>9.02</v>
+      </c>
     </row>
     <row r="104" ht="16.5" spans="1:3">
       <c r="A104" s="7">
         <v>46276</v>
       </c>
-      <c r="B104" s="3"/>
-      <c r="C104" s="3"/>
+      <c r="B104" s="3">
+        <v>8.7</v>
+      </c>
+      <c r="C104" s="3">
+        <v>10.07</v>
+      </c>
     </row>
     <row r="105" ht="16.5" spans="1:3">
       <c r="A105" s="7">
         <v>46277</v>
       </c>
-      <c r="B105" s="3"/>
-      <c r="C105" s="3"/>
+      <c r="B105" s="3">
+        <v>6.82</v>
+      </c>
+      <c r="C105" s="3">
+        <v>6.93</v>
+      </c>
     </row>
     <row r="106" ht="16.5" spans="1:3">
       <c r="A106" s="7">
         <v>46278</v>
       </c>
-      <c r="B106" s="3"/>
-      <c r="C106" s="3"/>
+      <c r="B106" s="3">
+        <v>11.11</v>
+      </c>
+      <c r="C106" s="5">
+        <v>5.2</v>
+      </c>
     </row>
     <row r="107" ht="16.5" spans="1:3">
       <c r="A107" s="7">
         <v>46279</v>
       </c>
-      <c r="B107" s="3"/>
-      <c r="C107" s="3"/>
+      <c r="B107" s="3">
+        <v>7.23</v>
+      </c>
+      <c r="C107" s="5">
+        <v>5.4</v>
+      </c>
     </row>
     <row r="108" ht="16.5" spans="1:3">
       <c r="A108" s="7">
         <v>46280</v>
       </c>
-      <c r="B108" s="3"/>
-      <c r="C108" s="3"/>
+      <c r="B108" s="3">
+        <v>6.54</v>
+      </c>
+      <c r="C108" s="3">
+        <v>8.42</v>
+      </c>
     </row>
     <row r="109" ht="16.5" spans="1:3">
       <c r="A109" s="7">
         <v>46281</v>
       </c>
-      <c r="B109" s="3"/>
-      <c r="C109" s="3"/>
+      <c r="B109" s="3">
+        <v>9.36</v>
+      </c>
+      <c r="C109" s="3">
+        <v>10.07</v>
+      </c>
     </row>
     <row r="110" ht="16.5" spans="1:3">
       <c r="A110" s="7">
         <v>46282</v>
       </c>
-      <c r="B110" s="3"/>
-      <c r="C110" s="3"/>
+      <c r="B110" s="3">
+        <v>20.75</v>
+      </c>
+      <c r="C110" s="3">
+        <v>13.43</v>
+      </c>
     </row>
     <row r="111" ht="16.5" spans="1:3">
       <c r="A111" s="7">
         <v>46283</v>
       </c>
-      <c r="B111" s="3"/>
-      <c r="C111" s="3"/>
+      <c r="B111" s="3">
+        <v>17.19</v>
+      </c>
+      <c r="C111" s="3">
+        <v>10.71</v>
+      </c>
     </row>
     <row r="112" ht="16.5" spans="1:3">
       <c r="A112" s="7">
         <v>46284</v>
       </c>
-      <c r="B112" s="3"/>
-      <c r="C112" s="3"/>
+      <c r="B112" s="3">
+        <v>6.18</v>
+      </c>
+      <c r="C112" s="3">
+        <v>5.47</v>
+      </c>
     </row>
     <row r="113" ht="16.5" spans="1:3">
       <c r="A113" s="7">
         <v>46285</v>
       </c>
-      <c r="B113" s="3"/>
-      <c r="C113" s="3"/>
+      <c r="B113" s="3">
+        <v>21.06</v>
+      </c>
+      <c r="C113" s="3">
+        <v>11.76</v>
+      </c>
     </row>
     <row r="114" ht="16.5" spans="1:3">
       <c r="A114" s="7">
         <v>46286</v>
       </c>
-      <c r="B114" s="3"/>
-      <c r="C114" s="3"/>
+      <c r="B114" s="3">
+        <v>19.33</v>
+      </c>
+      <c r="C114" s="3">
+        <v>9.83</v>
+      </c>
     </row>
     <row r="115" ht="16.5" spans="1:3">
       <c r="A115" s="7">
         <v>46287</v>
       </c>
-      <c r="B115" s="3"/>
-      <c r="C115" s="3"/>
+      <c r="B115" s="3">
+        <v>12.46</v>
+      </c>
+      <c r="C115" s="3">
+        <v>16.73</v>
+      </c>
     </row>
     <row r="116" ht="16.5" spans="1:3">
       <c r="A116" s="7">
         <v>46288</v>
       </c>
-      <c r="B116" s="3"/>
-      <c r="C116" s="3"/>
+      <c r="B116" s="3">
+        <v>17.49</v>
+      </c>
+      <c r="C116" s="3">
+        <v>16.88</v>
+      </c>
     </row>
     <row r="117" ht="16.5" spans="1:3">
       <c r="A117" s="7">
         <v>46289</v>
       </c>
-      <c r="B117" s="3"/>
-      <c r="C117" s="3"/>
+      <c r="B117" s="3">
+        <v>18.32</v>
+      </c>
+      <c r="C117" s="3">
+        <v>11.69</v>
+      </c>
     </row>
     <row r="118" ht="16.5" spans="1:3">
       <c r="A118" s="7">
         <v>46290</v>
       </c>
-      <c r="B118" s="3"/>
-      <c r="C118" s="3"/>
+      <c r="B118" s="3">
+        <v>16.03</v>
+      </c>
+      <c r="C118" s="3">
+        <v>8.41</v>
+      </c>
     </row>
     <row r="119" ht="16.5" spans="1:3">
       <c r="A119" s="7">
         <v>46291</v>
       </c>
-      <c r="B119" s="3"/>
-      <c r="C119" s="3"/>
+      <c r="B119" s="3">
+        <v>6.67</v>
+      </c>
+      <c r="C119" s="3">
+        <v>7.39</v>
+      </c>
     </row>
     <row r="120" ht="16.5" spans="1:3">
       <c r="A120" s="7">
         <v>46292</v>
       </c>
-      <c r="B120" s="3"/>
-      <c r="C120" s="3"/>
+      <c r="B120" s="3">
+        <v>5.47</v>
+      </c>
+      <c r="C120" s="3">
+        <v>7.83</v>
+      </c>
     </row>
     <row r="121" ht="16.5" spans="1:3">
       <c r="A121" s="7">
         <v>46293</v>
       </c>
-      <c r="B121" s="3"/>
-      <c r="C121" s="3"/>
+      <c r="B121" s="3">
+        <v>10.03</v>
+      </c>
+      <c r="C121" s="3">
+        <v>4.48</v>
+      </c>
     </row>
     <row r="122" ht="16.5" spans="1:3">
       <c r="A122" s="7">
         <v>46294</v>
       </c>
-      <c r="B122" s="3"/>
-      <c r="C122" s="3"/>
+      <c r="B122" s="3">
+        <v>5.58</v>
+      </c>
+      <c r="C122" s="3">
+        <v>3.89</v>
+      </c>
     </row>
     <row r="123" ht="16.5" spans="1:3">
       <c r="A123" s="7">
         <v>46295</v>
       </c>
-      <c r="B123" s="3"/>
-      <c r="C123" s="3"/>
+      <c r="B123" s="3">
+        <v>9.46</v>
+      </c>
+      <c r="C123" s="3">
+        <v>8.76</v>
+      </c>
     </row>
     <row r="124" ht="16.5" spans="1:3">
       <c r="A124" s="7">
         <v>46296</v>
       </c>
-      <c r="B124" s="3"/>
-      <c r="C124" s="3"/>
+      <c r="B124" s="3">
+        <v>18.64</v>
+      </c>
+      <c r="C124" s="3">
+        <v>4.43</v>
+      </c>
     </row>
     <row r="125" ht="16.5" spans="1:3">
       <c r="A125" s="7">
         <v>46297</v>
       </c>
-      <c r="B125" s="3"/>
-      <c r="C125" s="3"/>
+      <c r="B125" s="3">
+        <v>17.28</v>
+      </c>
+      <c r="C125" s="3">
+        <v>13.83</v>
+      </c>
     </row>
     <row r="126" ht="16.5" spans="1:3">
       <c r="A126" s="7">
         <v>46298</v>
       </c>
-      <c r="B126" s="3"/>
-      <c r="C126" s="3"/>
+      <c r="B126" s="3">
+        <v>11.36</v>
+      </c>
+      <c r="C126" s="3">
+        <v>7.26</v>
+      </c>
     </row>
     <row r="127" ht="16.5" spans="1:3">
       <c r="A127" s="7">
